--- a/output/pdf_financials_xlsx/GRD.xlsx
+++ b/output/pdf_financials_xlsx/GRD.xlsx
@@ -5135,34 +5135,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.016638</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.093211</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.179635</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.209092</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.210528</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.210528</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.33769</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.33769</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.280521</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.280521</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0.611447</v>
@@ -6430,16 +6430,16 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.520969</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.7373499999999999</v>
+        <v>0.601931</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.005</v>
+        <v>-0.133609</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.404738</v>
+        <v>0.380973</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.927224</v>
@@ -10662,7 +10662,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -11004,7 +11008,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11328,7 +11336,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>1.016638</v>
       </c>
@@ -20142,7 +20154,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRD.xlsx
+++ b/output/pdf_financials_xlsx/GRD.xlsx
@@ -974,43 +974,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000223</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>9.8e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000201</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000165</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00011</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.019249</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.016179</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.01076</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.003404</v>
       </c>
     </row>
     <row r="13">
@@ -1801,43 +1801,43 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.461316</v>
+        <v>-0.461415</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.939479</v>
+        <v>-0.939702</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.322264</v>
+        <v>-0.322362</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.449031</v>
+        <v>-0.449131</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.252607</v>
+        <v>-1.252687</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.5709880000000001</v>
+        <v>-0.5711889999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.449225</v>
+        <v>-0.44939</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.222423</v>
+        <v>-0.222533</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.175901</v>
+        <v>-0.175951</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.978543</v>
+        <v>-6.997792</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.187227</v>
+        <v>-4.203406</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.073898</v>
+        <v>-1.084658</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.302543</v>
+        <v>-0.305947</v>
       </c>
     </row>
     <row r="28">
@@ -1903,43 +1903,43 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.461316</v>
+        <v>-0.461415</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.939479</v>
+        <v>-0.939702</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.322264</v>
+        <v>-0.322362</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.449031</v>
+        <v>-0.449131</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.252607</v>
+        <v>-1.252687</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.5709880000000001</v>
+        <v>-0.5711889999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.449225</v>
+        <v>-0.44939</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.222423</v>
+        <v>-0.222533</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.175901</v>
+        <v>-0.175951</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.954813</v>
+        <v>-6.974062</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.081812</v>
+        <v>-4.097991</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.01579</v>
+        <v>-1.02655</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.29174</v>
+        <v>-0.295144</v>
       </c>
     </row>
     <row r="30">
@@ -1999,16 +1999,16 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-36130.77562470778</v>
+        <v>-36230.77562470778</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-25229.07472649731</v>
+        <v>-25329.07472649731</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-5365.7493000898</v>
+        <v>-5422.587290687233</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-229.7490982973965</v>
+        <v>-232.4297931990361</v>
       </c>
     </row>
     <row r="31">
@@ -2175,16 +2175,16 @@
         <v>0.007327</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.658016</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.193009</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.144971</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.04105</v>
       </c>
     </row>
     <row r="35">
@@ -2273,16 +2273,16 @@
         <v>0.007327</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.25</v>
+        <v>2.908016</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.193009</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.244971</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.14105</v>
       </c>
     </row>
     <row r="37">
@@ -2861,16 +2861,16 @@
         <v>0.000833</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.066331</v>
+        <v>0.408315</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.393294</v>
+        <v>0.200285</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.196701</v>
+        <v>0.05173</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.086982</v>
+        <v>0.045932</v>
       </c>
     </row>
     <row r="49">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10418,7 +10418,11 @@
           <t>Reclamation deposit (Note 4)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12160,7 +12164,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12676,7 +12684,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.005</v>
       </c>
@@ -21706,7 +21718,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -26678,7 +26690,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -32006,7 +32018,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -33626,7 +33638,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRD.xlsx
+++ b/output/pdf_financials_xlsx/GRD.xlsx
@@ -750,7 +750,7 @@
         <v>1.521892</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.356634</v>
+        <v>0.393817</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.246135</v>
@@ -6280,10 +6280,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.001181</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.00288</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -6295,13 +6295,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.019046</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.012808</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -17258,7 +17258,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -18234,7 +18238,11 @@
           <t>Proceeds on sales of marketable securities</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -18320,7 +18328,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -20508,7 +20520,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -22816,7 +22832,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
